--- a/artfynd/A 59985-2025 artfynd.xlsx
+++ b/artfynd/A 59985-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY13"/>
+  <dimension ref="A1:AY19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1837,6 +1837,674 @@
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>130325695</v>
+      </c>
+      <c r="B14" t="n">
+        <v>57823</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Mjösund, Boh</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>325798</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6431227</v>
+      </c>
+      <c r="S14" t="n">
+        <v>1</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Kungälv</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Romelanda</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2025-12-28</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>12:42</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2025-12-28</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>12:42</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Spår av födosök i träd</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Inka Eriksson</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Inka Eriksson</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>130320260</v>
+      </c>
+      <c r="B15" t="n">
+        <v>97783</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>224361</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Äkta lopplummer</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Huperzia europaea</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Björk</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Mjösund, Mjösund, Boh</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>325695</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6431179</v>
+      </c>
+      <c r="S15" t="n">
+        <v>20</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Kungälv</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Romelanda</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2025-12-22</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2025-12-22</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Anna Zeffer</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Anna Zeffer</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>130325538</v>
+      </c>
+      <c r="B16" t="n">
+        <v>57823</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Mjösund, Boh</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>325669</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6431314</v>
+      </c>
+      <c r="S16" t="n">
+        <v>5</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Kungälv</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Romelanda</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2025-12-28</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>13:04</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2025-12-28</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>13:04</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Spår av födosök i träd</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Inka Eriksson</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Inka Eriksson</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>130320281</v>
+      </c>
+      <c r="B17" t="n">
+        <v>97783</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>224361</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Äkta lopplummer</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Huperzia europaea</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Björk</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Mjösund, Mjösund, Boh</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>325750</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6431267</v>
+      </c>
+      <c r="S17" t="n">
+        <v>20</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Kungälv</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Romelanda</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2025-12-22</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2025-12-22</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Anna Zeffer</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Anna Zeffer</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>130325612</v>
+      </c>
+      <c r="B18" t="n">
+        <v>97783</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>224361</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Äkta lopplummer</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Huperzia europaea</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Björk</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Mjösund, Boh</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>325707</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6431230</v>
+      </c>
+      <c r="S18" t="n">
+        <v>5</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Kungälv</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Romelanda</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2025-12-28</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>12:51</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2025-12-28</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>12:51</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Växte på bergssida</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF18" t="inlineStr"/>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Inka Eriksson</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Inka Eriksson</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>130325581</v>
+      </c>
+      <c r="B19" t="n">
+        <v>96156</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>2810</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Västlig hakmossa</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Rhytidiadelphus loreus</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Hedw.) Warnst.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Mjösund, Boh</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>325704</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6431250</v>
+      </c>
+      <c r="S19" t="n">
+        <v>5</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Kungälv</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Romelanda</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2025-12-28</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>12:53</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2025-12-28</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>12:54</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>stora områden</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF19" t="inlineStr"/>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Inka Eriksson</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Inka Eriksson</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 59985-2025 artfynd.xlsx
+++ b/artfynd/A 59985-2025 artfynd.xlsx
@@ -1548,7 +1548,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>130313746</v>
+        <v>130313705</v>
       </c>
       <c r="B11" t="n">
         <v>96516</v>
@@ -1583,10 +1583,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>325661</v>
+        <v>325605</v>
       </c>
       <c r="R11" t="n">
-        <v>6431340</v>
+        <v>6431200</v>
       </c>
       <c r="S11" t="n">
         <v>20</v>
@@ -1645,7 +1645,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>130313705</v>
+        <v>130313746</v>
       </c>
       <c r="B12" t="n">
         <v>96516</v>
@@ -1680,10 +1680,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>325605</v>
+        <v>325661</v>
       </c>
       <c r="R12" t="n">
-        <v>6431200</v>
+        <v>6431340</v>
       </c>
       <c r="S12" t="n">
         <v>20</v>
@@ -2168,7 +2168,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>130320281</v>
+        <v>130325612</v>
       </c>
       <c r="B17" t="n">
         <v>97783</v>
@@ -2196,20 +2196,32 @@
           <t>Björk</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr"/>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Mjösund, Mjösund, Boh</t>
+          <t>Mjösund, Boh</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>325750</v>
+        <v>325707</v>
       </c>
       <c r="R17" t="n">
-        <v>6431267</v>
+        <v>6431230</v>
       </c>
       <c r="S17" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2233,12 +2245,27 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-12-22</t>
+          <t>2025-12-28</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2025-12-22</t>
+          <t>2025-12-28</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>12:51</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Växte på bergssida</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2247,25 +2274,26 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Anna Zeffer</t>
+          <t>Inka Eriksson</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Anna Zeffer</t>
+          <t>Inka Eriksson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>130325612</v>
+        <v>130320281</v>
       </c>
       <c r="B18" t="n">
         <v>97783</v>
@@ -2293,32 +2321,20 @@
           <t>Björk</t>
         </is>
       </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="N18" t="inlineStr"/>
+      <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Mjösund, Boh</t>
+          <t>Mjösund, Mjösund, Boh</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>325707</v>
+        <v>325750</v>
       </c>
       <c r="R18" t="n">
-        <v>6431230</v>
+        <v>6431267</v>
       </c>
       <c r="S18" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2342,27 +2358,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-12-28</t>
-        </is>
-      </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>12:51</t>
+          <t>2025-12-22</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2025-12-28</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>12:51</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Växte på bergssida</t>
+          <t>2025-12-22</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2371,19 +2372,18 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Inka Eriksson</t>
+          <t>Anna Zeffer</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Inka Eriksson</t>
+          <t>Anna Zeffer</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>

--- a/artfynd/A 59985-2025 artfynd.xlsx
+++ b/artfynd/A 59985-2025 artfynd.xlsx
@@ -2168,7 +2168,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>130325612</v>
+        <v>130320281</v>
       </c>
       <c r="B17" t="n">
         <v>97783</v>
@@ -2196,32 +2196,20 @@
           <t>Björk</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="N17" t="inlineStr"/>
+      <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Mjösund, Boh</t>
+          <t>Mjösund, Mjösund, Boh</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>325707</v>
+        <v>325750</v>
       </c>
       <c r="R17" t="n">
-        <v>6431230</v>
+        <v>6431267</v>
       </c>
       <c r="S17" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2245,27 +2233,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-12-28</t>
-        </is>
-      </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>12:51</t>
+          <t>2025-12-22</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2025-12-28</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>12:51</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Växte på bergssida</t>
+          <t>2025-12-22</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2274,26 +2247,25 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Inka Eriksson</t>
+          <t>Anna Zeffer</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Inka Eriksson</t>
+          <t>Anna Zeffer</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>130320281</v>
+        <v>130325612</v>
       </c>
       <c r="B18" t="n">
         <v>97783</v>
@@ -2321,20 +2293,32 @@
           <t>Björk</t>
         </is>
       </c>
-      <c r="I18" t="inlineStr"/>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Mjösund, Mjösund, Boh</t>
+          <t>Mjösund, Boh</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>325750</v>
+        <v>325707</v>
       </c>
       <c r="R18" t="n">
-        <v>6431267</v>
+        <v>6431230</v>
       </c>
       <c r="S18" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2358,12 +2342,27 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-12-22</t>
+          <t>2025-12-28</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2025-12-22</t>
+          <t>2025-12-28</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>12:51</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Växte på bergssida</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2372,18 +2371,19 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Anna Zeffer</t>
+          <t>Inka Eriksson</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Anna Zeffer</t>
+          <t>Inka Eriksson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>

--- a/artfynd/A 59985-2025 artfynd.xlsx
+++ b/artfynd/A 59985-2025 artfynd.xlsx
@@ -966,10 +966,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130307277</v>
+        <v>130307259</v>
       </c>
       <c r="B5" t="n">
-        <v>96156</v>
+        <v>96516</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -977,21 +977,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2810</v>
+        <v>2180</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1001,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>325663</v>
+        <v>325694</v>
       </c>
       <c r="R5" t="n">
-        <v>6431211</v>
+        <v>6431276</v>
       </c>
       <c r="S5" t="n">
         <v>20</v>
@@ -1063,10 +1063,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130307259</v>
+        <v>130307277</v>
       </c>
       <c r="B6" t="n">
-        <v>96516</v>
+        <v>96156</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1074,21 +1074,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2180</v>
+        <v>2810</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Hedw.) Warnst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1098,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>325694</v>
+        <v>325663</v>
       </c>
       <c r="R6" t="n">
-        <v>6431276</v>
+        <v>6431211</v>
       </c>
       <c r="S6" t="n">
         <v>20</v>

--- a/artfynd/A 59985-2025 artfynd.xlsx
+++ b/artfynd/A 59985-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130307242</v>
       </c>
       <c r="B2" t="n">
-        <v>96516</v>
+        <v>96519</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>130307331</v>
       </c>
       <c r="B3" t="n">
-        <v>96156</v>
+        <v>96159</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>130307212</v>
       </c>
       <c r="B4" t="n">
-        <v>96516</v>
+        <v>96519</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>130307259</v>
       </c>
       <c r="B5" t="n">
-        <v>96516</v>
+        <v>96519</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>130307277</v>
       </c>
       <c r="B6" t="n">
-        <v>96156</v>
+        <v>96159</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1163,7 +1163,7 @@
         <v>130307269</v>
       </c>
       <c r="B7" t="n">
-        <v>96516</v>
+        <v>96519</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1357,7 +1357,7 @@
         <v>130307222</v>
       </c>
       <c r="B9" t="n">
-        <v>96516</v>
+        <v>96519</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1454,7 +1454,7 @@
         <v>130313695</v>
       </c>
       <c r="B10" t="n">
-        <v>96516</v>
+        <v>96519</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1548,10 +1548,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>130313705</v>
+        <v>130313746</v>
       </c>
       <c r="B11" t="n">
-        <v>96516</v>
+        <v>96519</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1583,10 +1583,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>325605</v>
+        <v>325661</v>
       </c>
       <c r="R11" t="n">
-        <v>6431200</v>
+        <v>6431340</v>
       </c>
       <c r="S11" t="n">
         <v>20</v>
@@ -1645,10 +1645,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>130313746</v>
+        <v>130313705</v>
       </c>
       <c r="B12" t="n">
-        <v>96516</v>
+        <v>96519</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1680,10 +1680,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>325661</v>
+        <v>325605</v>
       </c>
       <c r="R12" t="n">
-        <v>6431340</v>
+        <v>6431200</v>
       </c>
       <c r="S12" t="n">
         <v>20</v>
@@ -1958,7 +1958,7 @@
         <v>130320260</v>
       </c>
       <c r="B15" t="n">
-        <v>97783</v>
+        <v>97786</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2171,7 +2171,7 @@
         <v>130320281</v>
       </c>
       <c r="B17" t="n">
-        <v>97783</v>
+        <v>97786</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2268,7 +2268,7 @@
         <v>130325612</v>
       </c>
       <c r="B18" t="n">
-        <v>97783</v>
+        <v>97786</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2393,7 +2393,7 @@
         <v>130325581</v>
       </c>
       <c r="B19" t="n">
-        <v>96156</v>
+        <v>96159</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>

--- a/artfynd/A 59985-2025 artfynd.xlsx
+++ b/artfynd/A 59985-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130307242</v>
       </c>
       <c r="B2" t="n">
-        <v>96519</v>
+        <v>96545</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>130307331</v>
       </c>
       <c r="B3" t="n">
-        <v>96159</v>
+        <v>96185</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>130307212</v>
       </c>
       <c r="B4" t="n">
-        <v>96519</v>
+        <v>96545</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>130307259</v>
       </c>
       <c r="B5" t="n">
-        <v>96519</v>
+        <v>96545</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>130307277</v>
       </c>
       <c r="B6" t="n">
-        <v>96159</v>
+        <v>96185</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1163,7 +1163,7 @@
         <v>130307269</v>
       </c>
       <c r="B7" t="n">
-        <v>96519</v>
+        <v>96545</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
         <v>130307394</v>
       </c>
       <c r="B8" t="n">
-        <v>57823</v>
+        <v>57849</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1357,7 +1357,7 @@
         <v>130307222</v>
       </c>
       <c r="B9" t="n">
-        <v>96519</v>
+        <v>96545</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1454,7 +1454,7 @@
         <v>130313695</v>
       </c>
       <c r="B10" t="n">
-        <v>96519</v>
+        <v>96545</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1548,10 +1548,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>130313746</v>
+        <v>130313705</v>
       </c>
       <c r="B11" t="n">
-        <v>96519</v>
+        <v>96545</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1583,10 +1583,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>325661</v>
+        <v>325605</v>
       </c>
       <c r="R11" t="n">
-        <v>6431340</v>
+        <v>6431200</v>
       </c>
       <c r="S11" t="n">
         <v>20</v>
@@ -1645,10 +1645,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>130313705</v>
+        <v>130313746</v>
       </c>
       <c r="B12" t="n">
-        <v>96519</v>
+        <v>96545</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1680,10 +1680,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>325605</v>
+        <v>325661</v>
       </c>
       <c r="R12" t="n">
-        <v>6431200</v>
+        <v>6431340</v>
       </c>
       <c r="S12" t="n">
         <v>20</v>
@@ -1745,7 +1745,7 @@
         <v>130313760</v>
       </c>
       <c r="B13" t="n">
-        <v>57823</v>
+        <v>57849</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1842,7 +1842,7 @@
         <v>130325695</v>
       </c>
       <c r="B14" t="n">
-        <v>57823</v>
+        <v>57849</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1958,7 +1958,7 @@
         <v>130320260</v>
       </c>
       <c r="B15" t="n">
-        <v>97786</v>
+        <v>97812</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2055,7 +2055,7 @@
         <v>130325538</v>
       </c>
       <c r="B16" t="n">
-        <v>57823</v>
+        <v>57849</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2171,7 +2171,7 @@
         <v>130320281</v>
       </c>
       <c r="B17" t="n">
-        <v>97786</v>
+        <v>97812</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2268,7 +2268,7 @@
         <v>130325612</v>
       </c>
       <c r="B18" t="n">
-        <v>97786</v>
+        <v>97812</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2393,7 +2393,7 @@
         <v>130325581</v>
       </c>
       <c r="B19" t="n">
-        <v>96159</v>
+        <v>96185</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>

--- a/artfynd/A 59985-2025 artfynd.xlsx
+++ b/artfynd/A 59985-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130307242</v>
       </c>
       <c r="B2" t="n">
-        <v>96545</v>
+        <v>96546</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>130307331</v>
       </c>
       <c r="B3" t="n">
-        <v>96185</v>
+        <v>96186</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>130307212</v>
       </c>
       <c r="B4" t="n">
-        <v>96545</v>
+        <v>96546</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>130307259</v>
       </c>
       <c r="B5" t="n">
-        <v>96545</v>
+        <v>96546</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>130307277</v>
       </c>
       <c r="B6" t="n">
-        <v>96185</v>
+        <v>96186</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1163,7 +1163,7 @@
         <v>130307269</v>
       </c>
       <c r="B7" t="n">
-        <v>96545</v>
+        <v>96546</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1357,7 +1357,7 @@
         <v>130307222</v>
       </c>
       <c r="B9" t="n">
-        <v>96545</v>
+        <v>96546</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1454,7 +1454,7 @@
         <v>130313695</v>
       </c>
       <c r="B10" t="n">
-        <v>96545</v>
+        <v>96546</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1551,7 +1551,7 @@
         <v>130313705</v>
       </c>
       <c r="B11" t="n">
-        <v>96545</v>
+        <v>96546</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1648,7 +1648,7 @@
         <v>130313746</v>
       </c>
       <c r="B12" t="n">
-        <v>96545</v>
+        <v>96546</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1958,7 +1958,7 @@
         <v>130320260</v>
       </c>
       <c r="B15" t="n">
-        <v>97812</v>
+        <v>97813</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2171,7 +2171,7 @@
         <v>130320281</v>
       </c>
       <c r="B17" t="n">
-        <v>97812</v>
+        <v>97813</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2268,7 +2268,7 @@
         <v>130325612</v>
       </c>
       <c r="B18" t="n">
-        <v>97812</v>
+        <v>97813</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2393,7 +2393,7 @@
         <v>130325581</v>
       </c>
       <c r="B19" t="n">
-        <v>96185</v>
+        <v>96186</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>

--- a/artfynd/A 59985-2025 artfynd.xlsx
+++ b/artfynd/A 59985-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130307242</v>
       </c>
       <c r="B2" t="n">
-        <v>96546</v>
+        <v>96547</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>130307331</v>
       </c>
       <c r="B3" t="n">
-        <v>96186</v>
+        <v>96187</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>130307212</v>
       </c>
       <c r="B4" t="n">
-        <v>96546</v>
+        <v>96547</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>130307259</v>
       </c>
       <c r="B5" t="n">
-        <v>96546</v>
+        <v>96547</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>130307277</v>
       </c>
       <c r="B6" t="n">
-        <v>96186</v>
+        <v>96187</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1163,7 +1163,7 @@
         <v>130307269</v>
       </c>
       <c r="B7" t="n">
-        <v>96546</v>
+        <v>96547</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1357,7 +1357,7 @@
         <v>130307222</v>
       </c>
       <c r="B9" t="n">
-        <v>96546</v>
+        <v>96547</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1454,7 +1454,7 @@
         <v>130313695</v>
       </c>
       <c r="B10" t="n">
-        <v>96546</v>
+        <v>96547</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1551,7 +1551,7 @@
         <v>130313705</v>
       </c>
       <c r="B11" t="n">
-        <v>96546</v>
+        <v>96547</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1648,7 +1648,7 @@
         <v>130313746</v>
       </c>
       <c r="B12" t="n">
-        <v>96546</v>
+        <v>96547</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1958,7 +1958,7 @@
         <v>130320260</v>
       </c>
       <c r="B15" t="n">
-        <v>97813</v>
+        <v>97814</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2171,7 +2171,7 @@
         <v>130320281</v>
       </c>
       <c r="B17" t="n">
-        <v>97813</v>
+        <v>97814</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2268,7 +2268,7 @@
         <v>130325612</v>
       </c>
       <c r="B18" t="n">
-        <v>97813</v>
+        <v>97814</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2393,7 +2393,7 @@
         <v>130325581</v>
       </c>
       <c r="B19" t="n">
-        <v>96186</v>
+        <v>96187</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>

--- a/artfynd/A 59985-2025 artfynd.xlsx
+++ b/artfynd/A 59985-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130307242</v>
       </c>
       <c r="B2" t="n">
-        <v>96547</v>
+        <v>96549</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>130307331</v>
       </c>
       <c r="B3" t="n">
-        <v>96187</v>
+        <v>96189</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>130307212</v>
       </c>
       <c r="B4" t="n">
-        <v>96547</v>
+        <v>96549</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>130307259</v>
       </c>
       <c r="B5" t="n">
-        <v>96547</v>
+        <v>96549</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>130307277</v>
       </c>
       <c r="B6" t="n">
-        <v>96187</v>
+        <v>96189</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1163,7 +1163,7 @@
         <v>130307269</v>
       </c>
       <c r="B7" t="n">
-        <v>96547</v>
+        <v>96549</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
         <v>130307394</v>
       </c>
       <c r="B8" t="n">
-        <v>57849</v>
+        <v>57851</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1357,7 +1357,7 @@
         <v>130307222</v>
       </c>
       <c r="B9" t="n">
-        <v>96547</v>
+        <v>96549</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1454,7 +1454,7 @@
         <v>130313695</v>
       </c>
       <c r="B10" t="n">
-        <v>96547</v>
+        <v>96549</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1551,7 +1551,7 @@
         <v>130313705</v>
       </c>
       <c r="B11" t="n">
-        <v>96547</v>
+        <v>96549</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1648,7 +1648,7 @@
         <v>130313746</v>
       </c>
       <c r="B12" t="n">
-        <v>96547</v>
+        <v>96549</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1745,7 +1745,7 @@
         <v>130313760</v>
       </c>
       <c r="B13" t="n">
-        <v>57849</v>
+        <v>57851</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1842,7 +1842,7 @@
         <v>130325695</v>
       </c>
       <c r="B14" t="n">
-        <v>57849</v>
+        <v>57851</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1958,7 +1958,7 @@
         <v>130320260</v>
       </c>
       <c r="B15" t="n">
-        <v>97814</v>
+        <v>97816</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2055,7 +2055,7 @@
         <v>130325538</v>
       </c>
       <c r="B16" t="n">
-        <v>57849</v>
+        <v>57851</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2171,7 +2171,7 @@
         <v>130320281</v>
       </c>
       <c r="B17" t="n">
-        <v>97814</v>
+        <v>97816</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2268,7 +2268,7 @@
         <v>130325612</v>
       </c>
       <c r="B18" t="n">
-        <v>97814</v>
+        <v>97816</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2393,7 +2393,7 @@
         <v>130325581</v>
       </c>
       <c r="B19" t="n">
-        <v>96187</v>
+        <v>96189</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>

--- a/artfynd/A 59985-2025 artfynd.xlsx
+++ b/artfynd/A 59985-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130307242</v>
       </c>
       <c r="B2" t="n">
-        <v>96549</v>
+        <v>96553</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>130307331</v>
       </c>
       <c r="B3" t="n">
-        <v>96189</v>
+        <v>96193</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>130307212</v>
       </c>
       <c r="B4" t="n">
-        <v>96549</v>
+        <v>96553</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>130307259</v>
       </c>
       <c r="B5" t="n">
-        <v>96549</v>
+        <v>96553</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>130307277</v>
       </c>
       <c r="B6" t="n">
-        <v>96189</v>
+        <v>96193</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1163,7 +1163,7 @@
         <v>130307269</v>
       </c>
       <c r="B7" t="n">
-        <v>96549</v>
+        <v>96553</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1357,7 +1357,7 @@
         <v>130307222</v>
       </c>
       <c r="B9" t="n">
-        <v>96549</v>
+        <v>96553</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1454,7 +1454,7 @@
         <v>130313695</v>
       </c>
       <c r="B10" t="n">
-        <v>96549</v>
+        <v>96553</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1551,7 +1551,7 @@
         <v>130313705</v>
       </c>
       <c r="B11" t="n">
-        <v>96549</v>
+        <v>96553</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1648,7 +1648,7 @@
         <v>130313746</v>
       </c>
       <c r="B12" t="n">
-        <v>96549</v>
+        <v>96553</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1958,7 +1958,7 @@
         <v>130320260</v>
       </c>
       <c r="B15" t="n">
-        <v>97816</v>
+        <v>97820</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2171,7 +2171,7 @@
         <v>130320281</v>
       </c>
       <c r="B17" t="n">
-        <v>97816</v>
+        <v>97820</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2268,7 +2268,7 @@
         <v>130325612</v>
       </c>
       <c r="B18" t="n">
-        <v>97816</v>
+        <v>97820</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2393,7 +2393,7 @@
         <v>130325581</v>
       </c>
       <c r="B19" t="n">
-        <v>96189</v>
+        <v>96193</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>

--- a/artfynd/A 59985-2025 artfynd.xlsx
+++ b/artfynd/A 59985-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130307242</v>
       </c>
       <c r="B2" t="n">
-        <v>96553</v>
+        <v>96566</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>130307331</v>
       </c>
       <c r="B3" t="n">
-        <v>96193</v>
+        <v>96206</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>130307212</v>
       </c>
       <c r="B4" t="n">
-        <v>96553</v>
+        <v>96566</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>130307259</v>
       </c>
       <c r="B5" t="n">
-        <v>96553</v>
+        <v>96566</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>130307277</v>
       </c>
       <c r="B6" t="n">
-        <v>96193</v>
+        <v>96206</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1163,7 +1163,7 @@
         <v>130307269</v>
       </c>
       <c r="B7" t="n">
-        <v>96553</v>
+        <v>96566</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
         <v>130307394</v>
       </c>
       <c r="B8" t="n">
-        <v>57851</v>
+        <v>57859</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1357,7 +1357,7 @@
         <v>130307222</v>
       </c>
       <c r="B9" t="n">
-        <v>96553</v>
+        <v>96566</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1454,7 +1454,7 @@
         <v>130313695</v>
       </c>
       <c r="B10" t="n">
-        <v>96553</v>
+        <v>96566</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1551,7 +1551,7 @@
         <v>130313705</v>
       </c>
       <c r="B11" t="n">
-        <v>96553</v>
+        <v>96566</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1648,7 +1648,7 @@
         <v>130313746</v>
       </c>
       <c r="B12" t="n">
-        <v>96553</v>
+        <v>96566</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1745,7 +1745,7 @@
         <v>130313760</v>
       </c>
       <c r="B13" t="n">
-        <v>57851</v>
+        <v>57859</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1842,7 +1842,7 @@
         <v>130325695</v>
       </c>
       <c r="B14" t="n">
-        <v>57851</v>
+        <v>57859</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1958,7 +1958,7 @@
         <v>130320260</v>
       </c>
       <c r="B15" t="n">
-        <v>97820</v>
+        <v>97833</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2055,7 +2055,7 @@
         <v>130325538</v>
       </c>
       <c r="B16" t="n">
-        <v>57851</v>
+        <v>57859</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2171,7 +2171,7 @@
         <v>130320281</v>
       </c>
       <c r="B17" t="n">
-        <v>97820</v>
+        <v>97833</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2268,7 +2268,7 @@
         <v>130325612</v>
       </c>
       <c r="B18" t="n">
-        <v>97820</v>
+        <v>97833</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2393,7 +2393,7 @@
         <v>130325581</v>
       </c>
       <c r="B19" t="n">
-        <v>96193</v>
+        <v>96206</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>

--- a/artfynd/A 59985-2025 artfynd.xlsx
+++ b/artfynd/A 59985-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130307242</v>
       </c>
       <c r="B2" t="n">
-        <v>96566</v>
+        <v>96567</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>130307331</v>
       </c>
       <c r="B3" t="n">
-        <v>96206</v>
+        <v>96207</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>130307212</v>
       </c>
       <c r="B4" t="n">
-        <v>96566</v>
+        <v>96567</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>130307259</v>
       </c>
       <c r="B5" t="n">
-        <v>96566</v>
+        <v>96567</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>130307277</v>
       </c>
       <c r="B6" t="n">
-        <v>96206</v>
+        <v>96207</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1163,7 +1163,7 @@
         <v>130307269</v>
       </c>
       <c r="B7" t="n">
-        <v>96566</v>
+        <v>96567</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
         <v>130307394</v>
       </c>
       <c r="B8" t="n">
-        <v>57859</v>
+        <v>57860</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1357,7 +1357,7 @@
         <v>130307222</v>
       </c>
       <c r="B9" t="n">
-        <v>96566</v>
+        <v>96567</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1454,7 +1454,7 @@
         <v>130313695</v>
       </c>
       <c r="B10" t="n">
-        <v>96566</v>
+        <v>96567</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1551,7 +1551,7 @@
         <v>130313705</v>
       </c>
       <c r="B11" t="n">
-        <v>96566</v>
+        <v>96567</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1648,7 +1648,7 @@
         <v>130313746</v>
       </c>
       <c r="B12" t="n">
-        <v>96566</v>
+        <v>96567</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1745,7 +1745,7 @@
         <v>130313760</v>
       </c>
       <c r="B13" t="n">
-        <v>57859</v>
+        <v>57860</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1842,7 +1842,7 @@
         <v>130325695</v>
       </c>
       <c r="B14" t="n">
-        <v>57859</v>
+        <v>57860</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1958,7 +1958,7 @@
         <v>130320260</v>
       </c>
       <c r="B15" t="n">
-        <v>97833</v>
+        <v>97834</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2055,7 +2055,7 @@
         <v>130325538</v>
       </c>
       <c r="B16" t="n">
-        <v>57859</v>
+        <v>57860</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2171,7 +2171,7 @@
         <v>130320281</v>
       </c>
       <c r="B17" t="n">
-        <v>97833</v>
+        <v>97834</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2268,7 +2268,7 @@
         <v>130325612</v>
       </c>
       <c r="B18" t="n">
-        <v>97833</v>
+        <v>97834</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2393,7 +2393,7 @@
         <v>130325581</v>
       </c>
       <c r="B19" t="n">
-        <v>96206</v>
+        <v>96207</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>

--- a/artfynd/A 59985-2025 artfynd.xlsx
+++ b/artfynd/A 59985-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130307242</v>
       </c>
       <c r="B2" t="n">
-        <v>96567</v>
+        <v>96570</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>130307331</v>
       </c>
       <c r="B3" t="n">
-        <v>96207</v>
+        <v>96210</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>130307212</v>
       </c>
       <c r="B4" t="n">
-        <v>96567</v>
+        <v>96570</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>130307259</v>
       </c>
       <c r="B5" t="n">
-        <v>96567</v>
+        <v>96570</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>130307277</v>
       </c>
       <c r="B6" t="n">
-        <v>96207</v>
+        <v>96210</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1163,7 +1163,7 @@
         <v>130307269</v>
       </c>
       <c r="B7" t="n">
-        <v>96567</v>
+        <v>96570</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
         <v>130307394</v>
       </c>
       <c r="B8" t="n">
-        <v>57860</v>
+        <v>57861</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1357,7 +1357,7 @@
         <v>130307222</v>
       </c>
       <c r="B9" t="n">
-        <v>96567</v>
+        <v>96570</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1454,7 +1454,7 @@
         <v>130313695</v>
       </c>
       <c r="B10" t="n">
-        <v>96567</v>
+        <v>96570</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1551,7 +1551,7 @@
         <v>130313705</v>
       </c>
       <c r="B11" t="n">
-        <v>96567</v>
+        <v>96570</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1648,7 +1648,7 @@
         <v>130313746</v>
       </c>
       <c r="B12" t="n">
-        <v>96567</v>
+        <v>96570</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1745,7 +1745,7 @@
         <v>130313760</v>
       </c>
       <c r="B13" t="n">
-        <v>57860</v>
+        <v>57861</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1842,7 +1842,7 @@
         <v>130325695</v>
       </c>
       <c r="B14" t="n">
-        <v>57860</v>
+        <v>57861</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1958,7 +1958,7 @@
         <v>130320260</v>
       </c>
       <c r="B15" t="n">
-        <v>97834</v>
+        <v>97837</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2055,7 +2055,7 @@
         <v>130325538</v>
       </c>
       <c r="B16" t="n">
-        <v>57860</v>
+        <v>57861</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2171,7 +2171,7 @@
         <v>130320281</v>
       </c>
       <c r="B17" t="n">
-        <v>97834</v>
+        <v>97837</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2268,7 +2268,7 @@
         <v>130325612</v>
       </c>
       <c r="B18" t="n">
-        <v>97834</v>
+        <v>97837</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2393,7 +2393,7 @@
         <v>130325581</v>
       </c>
       <c r="B19" t="n">
-        <v>96207</v>
+        <v>96210</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>

--- a/artfynd/A 59985-2025 artfynd.xlsx
+++ b/artfynd/A 59985-2025 artfynd.xlsx
@@ -966,10 +966,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130307259</v>
+        <v>130307277</v>
       </c>
       <c r="B5" t="n">
-        <v>96570</v>
+        <v>96210</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -977,21 +977,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2180</v>
+        <v>2810</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Hedw.) Warnst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1001,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>325694</v>
+        <v>325663</v>
       </c>
       <c r="R5" t="n">
-        <v>6431276</v>
+        <v>6431211</v>
       </c>
       <c r="S5" t="n">
         <v>20</v>
@@ -1063,10 +1063,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130307277</v>
+        <v>130307259</v>
       </c>
       <c r="B6" t="n">
-        <v>96210</v>
+        <v>96570</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1074,21 +1074,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2810</v>
+        <v>2180</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1098,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>325663</v>
+        <v>325694</v>
       </c>
       <c r="R6" t="n">
-        <v>6431211</v>
+        <v>6431276</v>
       </c>
       <c r="S6" t="n">
         <v>20</v>

--- a/artfynd/A 59985-2025 artfynd.xlsx
+++ b/artfynd/A 59985-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY19"/>
+  <dimension ref="A1:AY20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>130307242</v>
+        <v>130297877</v>
       </c>
       <c r="B2" t="n">
-        <v>96570</v>
+        <v>96708</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -710,13 +710,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>325669</v>
+        <v>325872</v>
       </c>
       <c r="R2" t="n">
-        <v>6431163</v>
+        <v>6431294</v>
       </c>
       <c r="S2" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130307331</v>
+        <v>130307212</v>
       </c>
       <c r="B3" t="n">
-        <v>96210</v>
+        <v>96708</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2810</v>
+        <v>2180</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>325720</v>
+        <v>325660</v>
       </c>
       <c r="R3" t="n">
-        <v>6431285</v>
+        <v>6431186</v>
       </c>
       <c r="S3" t="n">
         <v>20</v>
@@ -869,10 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130307212</v>
+        <v>130307222</v>
       </c>
       <c r="B4" t="n">
-        <v>96570</v>
+        <v>96708</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>325660</v>
+        <v>325718</v>
       </c>
       <c r="R4" t="n">
-        <v>6431186</v>
+        <v>6431181</v>
       </c>
       <c r="S4" t="n">
         <v>20</v>
@@ -966,10 +966,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130307277</v>
+        <v>130307242</v>
       </c>
       <c r="B5" t="n">
-        <v>96210</v>
+        <v>96708</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -977,21 +977,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2810</v>
+        <v>2180</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1001,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>325663</v>
+        <v>325669</v>
       </c>
       <c r="R5" t="n">
-        <v>6431211</v>
+        <v>6431163</v>
       </c>
       <c r="S5" t="n">
         <v>20</v>
@@ -1066,7 +1066,7 @@
         <v>130307259</v>
       </c>
       <c r="B6" t="n">
-        <v>96570</v>
+        <v>96708</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1163,7 +1163,7 @@
         <v>130307269</v>
       </c>
       <c r="B7" t="n">
-        <v>96570</v>
+        <v>96708</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1257,45 +1257,45 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130307394</v>
+        <v>130313695</v>
       </c>
       <c r="B8" t="n">
-        <v>57861</v>
+        <v>96708</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100049</v>
+        <v>2180</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Kroppkärr, Kroppkärr, Boh</t>
+          <t>Mjösund, Mjösund, Boh</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>325703</v>
+        <v>325649</v>
       </c>
       <c r="R8" t="n">
-        <v>6431316</v>
+        <v>6431224</v>
       </c>
       <c r="S8" t="n">
         <v>20</v>
@@ -1354,10 +1354,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>130307222</v>
+        <v>130313705</v>
       </c>
       <c r="B9" t="n">
-        <v>96570</v>
+        <v>96708</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1385,14 +1385,14 @@
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Kroppkärr, Kroppkärr, Boh</t>
+          <t>Mjösund, Mjösund, Boh</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>325718</v>
+        <v>325605</v>
       </c>
       <c r="R9" t="n">
-        <v>6431181</v>
+        <v>6431200</v>
       </c>
       <c r="S9" t="n">
         <v>20</v>
@@ -1451,10 +1451,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>130313695</v>
+        <v>130313746</v>
       </c>
       <c r="B10" t="n">
-        <v>96570</v>
+        <v>96708</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1486,10 +1486,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>325649</v>
+        <v>325661</v>
       </c>
       <c r="R10" t="n">
-        <v>6431224</v>
+        <v>6431340</v>
       </c>
       <c r="S10" t="n">
         <v>20</v>
@@ -1548,10 +1548,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>130313705</v>
+        <v>130307277</v>
       </c>
       <c r="B11" t="n">
-        <v>96570</v>
+        <v>96348</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1559,34 +1559,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>2180</v>
+        <v>2810</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Hedw.) Warnst.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Mjösund, Mjösund, Boh</t>
+          <t>Kroppkärr, Kroppkärr, Boh</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>325605</v>
+        <v>325663</v>
       </c>
       <c r="R11" t="n">
-        <v>6431200</v>
+        <v>6431211</v>
       </c>
       <c r="S11" t="n">
         <v>20</v>
@@ -1645,10 +1645,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>130313746</v>
+        <v>130307331</v>
       </c>
       <c r="B12" t="n">
-        <v>96570</v>
+        <v>96348</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1656,34 +1656,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>2180</v>
+        <v>2810</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Hedw.) Warnst.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Mjösund, Mjösund, Boh</t>
+          <t>Kroppkärr, Kroppkärr, Boh</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>325661</v>
+        <v>325720</v>
       </c>
       <c r="R12" t="n">
-        <v>6431340</v>
+        <v>6431285</v>
       </c>
       <c r="S12" t="n">
         <v>20</v>
@@ -1742,48 +1742,52 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>130313760</v>
+        <v>130325581</v>
       </c>
       <c r="B13" t="n">
-        <v>57861</v>
+        <v>96348</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100049</v>
+        <v>2810</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) Warnst.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Mjösund, Mjösund, Boh</t>
+          <t>Mjösund, Boh</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>325761</v>
+        <v>325704</v>
       </c>
       <c r="R13" t="n">
-        <v>6431296</v>
+        <v>6431250</v>
       </c>
       <c r="S13" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1807,12 +1811,27 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-12-22</t>
+          <t>2025-12-28</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2025-12-22</t>
+          <t>2025-12-28</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>12:54</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>stora områden</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1821,32 +1840,33 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Anna Zeffer</t>
+          <t>Inka Eriksson</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Anna Zeffer</t>
+          <t>Inka Eriksson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>130325695</v>
+        <v>130307394</v>
       </c>
       <c r="B14" t="n">
-        <v>57861</v>
+        <v>57950</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
@@ -1868,23 +1888,19 @@
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr"/>
-      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Mjösund, Boh</t>
+          <t>Kroppkärr, Kroppkärr, Boh</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>325798</v>
+        <v>325703</v>
       </c>
       <c r="R14" t="n">
-        <v>6431227</v>
+        <v>6431316</v>
       </c>
       <c r="S14" t="n">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -1908,27 +1924,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-12-28</t>
-        </is>
-      </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>12:42</t>
+          <t>2025-12-22</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2025-12-28</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>12:42</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Spår av födosök i träd</t>
+          <t>2025-12-22</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -1943,22 +1944,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Inka Eriksson</t>
+          <t>Anna Zeffer</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Inka Eriksson</t>
+          <t>Anna Zeffer</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>130320260</v>
+        <v>130313760</v>
       </c>
       <c r="B15" t="n">
-        <v>97837</v>
+        <v>57950</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1966,21 +1967,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>224361</v>
+        <v>100049</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Äkta lopplummer</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Huperzia europaea</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Björk</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -1990,10 +1991,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>325695</v>
+        <v>325761</v>
       </c>
       <c r="R15" t="n">
-        <v>6431179</v>
+        <v>6431296</v>
       </c>
       <c r="S15" t="n">
         <v>20</v>
@@ -2055,11 +2056,11 @@
         <v>130325538</v>
       </c>
       <c r="B16" t="n">
-        <v>57861</v>
+        <v>57950</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
@@ -2168,10 +2169,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>130320281</v>
+        <v>130325695</v>
       </c>
       <c r="B17" t="n">
-        <v>97837</v>
+        <v>57950</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2179,37 +2180,41 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>224361</v>
+        <v>100049</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Äkta lopplummer</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Huperzia europaea</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Björk</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Mjösund, Mjösund, Boh</t>
+          <t>Mjösund, Boh</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>325750</v>
+        <v>325798</v>
       </c>
       <c r="R17" t="n">
-        <v>6431267</v>
+        <v>6431227</v>
       </c>
       <c r="S17" t="n">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2233,12 +2238,27 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-12-22</t>
+          <t>2025-12-28</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2025-12-22</t>
+          <t>2025-12-28</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>12:42</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Spår av födosök i träd</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2253,22 +2273,22 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Anna Zeffer</t>
+          <t>Inka Eriksson</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Anna Zeffer</t>
+          <t>Inka Eriksson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>130325612</v>
+        <v>130320260</v>
       </c>
       <c r="B18" t="n">
-        <v>97837</v>
+        <v>97975</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2293,32 +2313,20 @@
           <t>Björk</t>
         </is>
       </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="N18" t="inlineStr"/>
+      <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Mjösund, Boh</t>
+          <t>Mjösund, Mjösund, Boh</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>325707</v>
+        <v>325695</v>
       </c>
       <c r="R18" t="n">
-        <v>6431230</v>
+        <v>6431179</v>
       </c>
       <c r="S18" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2342,27 +2350,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-12-28</t>
-        </is>
-      </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>12:51</t>
+          <t>2025-12-22</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2025-12-28</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>12:51</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Växte på bergssida</t>
+          <t>2025-12-22</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2371,29 +2364,28 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Inka Eriksson</t>
+          <t>Anna Zeffer</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Inka Eriksson</t>
+          <t>Anna Zeffer</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>130325581</v>
+        <v>130320281</v>
       </c>
       <c r="B19" t="n">
-        <v>96210</v>
+        <v>97975</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2401,41 +2393,37 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>2810</v>
+        <v>224361</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Äkta lopplummer</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Huperzia europaea</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
+          <t>Björk</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Mjösund, Boh</t>
+          <t>Mjösund, Mjösund, Boh</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>325704</v>
+        <v>325750</v>
       </c>
       <c r="R19" t="n">
-        <v>6431250</v>
+        <v>6431267</v>
       </c>
       <c r="S19" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2459,27 +2447,12 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-12-28</t>
-        </is>
-      </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>12:53</t>
+          <t>2025-12-22</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2025-12-28</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>12:54</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>stora områden</t>
+          <t>2025-12-22</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2488,22 +2461,146 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
+          <t>Anna Zeffer</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Anna Zeffer</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>130325612</v>
+      </c>
+      <c r="B20" t="n">
+        <v>97975</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>224361</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Äkta lopplummer</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Huperzia europaea</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Björk</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Mjösund, Boh</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>325707</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6431230</v>
+      </c>
+      <c r="S20" t="n">
+        <v>5</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Kungälv</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Romelanda</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2025-12-28</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>12:51</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2025-12-28</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>12:51</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Växte på bergssida</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF20" t="inlineStr"/>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
           <t>Inka Eriksson</t>
         </is>
       </c>
-      <c r="AX19" t="inlineStr">
+      <c r="AX20" t="inlineStr">
         <is>
           <t>Inka Eriksson</t>
         </is>
       </c>
-      <c r="AY19" t="inlineStr"/>
+      <c r="AY20" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 59985-2025 artfynd.xlsx
+++ b/artfynd/A 59985-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY20"/>
+  <dimension ref="A1:AZ20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130297877</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130307212</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130307222</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1060,6 +1080,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130307242</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1157,6 +1182,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130307259</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1254,6 +1284,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130307269</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1351,6 +1386,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130313695</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1448,6 +1488,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130313705</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1545,6 +1590,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130313746</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1642,6 +1692,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130307277</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1739,6 +1794,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130307331</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1856,6 +1916,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130325581</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1953,6 +2018,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130307394</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2050,6 +2120,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130313760</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2166,6 +2241,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130325538</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2282,6 +2362,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130325695</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2379,6 +2464,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130320260</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2476,6 +2566,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130320281</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2601,8 +2696,34 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130325612</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>